--- a/samples/ss_tasik_ingest.xlsx
+++ b/samples/ss_tasik_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_tasik_ingest.xlsx
+++ b/samples/ss_tasik_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Tasikmalaya Baru 500/150 kV</t>
+          <t>IBT 1 Tasikmalaya Baru 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,31 +734,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tasikmalaya Baru (bus 150 kV)</t>
+          <t>IBT 2 Tasikmalaya Baru 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 2 TSBRU7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TSBRU7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>TSBRU</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -774,10 +784,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -791,17 +805,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PLTP Darajat</t>
+          <t>Tasikmalaya Baru (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KIT_DRJAT</t>
+          <t>TSBRU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -844,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLTP Kamojang / Karaha</t>
+          <t>PLTP Darajat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KIT_KRAHA</t>
+          <t>KIT_DRJAT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -897,21 +911,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Garut</t>
+          <t>PLTP Kamojang / Karaha</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GARUT</t>
+          <t>KIT_KRAHA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -950,12 +964,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tasikmalaya</t>
+          <t>Garut</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TSMYA</t>
+          <t>GARUT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -986,14 +1000,10 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1007,12 +1017,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Karangnunggal</t>
+          <t>Tasikmalaya</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KRNGL</t>
+          <t>TSMYA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1043,10 +1053,14 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1060,12 +1074,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ciamis</t>
+          <t>Karangnunggal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CAMIS</t>
+          <t>KRNGL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1074,7 +1088,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1113,12 +1127,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Banjar</t>
+          <t>Ciamis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNJAR</t>
+          <t>CAMIS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1127,7 +1141,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1149,14 +1163,10 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1170,51 +1180,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Tasikmalaya</t>
+          <t>Banjar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IBT 1 TSMYA</t>
+          <t>BNJAR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>TSMYA</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>TSMYA4</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
@@ -1224,10 +1216,14 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1241,17 +1237,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tasikmalaya (bus 70 kV)</t>
+          <t>IBT 150/70 kV Tasikmalaya</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TSMYA4</t>
+          <t>IBT 1 TSMYA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1259,15 +1255,33 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TSMYA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TSMYA4</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>IBT 150/70 kV</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -1294,12 +1308,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Malangbong</t>
+          <t>Tasikmalaya (bus 70 kV)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MLBNG</t>
+          <t>TSMYA4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1308,7 +1322,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1330,14 +1344,10 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1351,12 +1361,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pangandaran</t>
+          <t>Malangbong</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PDRAN</t>
+          <t>MLBNG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1365,7 +1375,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1377,11 +1387,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>ujung subsistem</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
@@ -1396,7 +1402,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1412,12 +1418,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kamojang (SS New Ujungberung)</t>
+          <t>Pangandaran</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KMJNG</t>
+          <t>PDRAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1426,11 +1432,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1440,7 +1446,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Bandung Selatan 1,2 - New Ujungberung 1,2</t>
+          <t>ujung subsistem</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1449,17 +1455,17 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1473,12 +1479,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Majenang (UP2B Jateng)</t>
+          <t>Kamojang (SS New Ujungberung)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MNANG</t>
+          <t>KMJNG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1487,7 +1493,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1501,7 +1507,7 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Kesugihan 1,2 (UP2B Jateng &amp; DIY)</t>
+          <t>batas ke Subsistem Bandung Selatan 1,2 - New Ujungberung 1,2</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1527,6 +1533,67 @@
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Majenang (UP2B Jateng)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MNANG</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Kesugihan 1,2 (UP2B Jateng &amp; DIY)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2461,12 +2528,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[N-1] GI 70 kV Pangandaran hanya beroperasi 1 Busbar sehingga kesulitan dalam melakukan pemeliharaan (Peralatan GI banyak mengalami korosif, karena lokasi GI dekat pantai)</t>
+          <t>[BELUM_DITETAPKAN] GI 70 kV Pangandaran hanya beroperasi 1 Busbar sehingga kesulitan dalam melakukan pemeliharaan (Peralatan GI banyak mengalami korosif, karena lokasi GI dekat pantai)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">

--- a/samples/ss_tasik_ingest.xlsx
+++ b/samples/ss_tasik_ingest.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gardu_Induk_dan_Aset" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jalur_Transmisi" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bay" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2372,6 +2373,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kode GI</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nama GI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Feeder (GI Induk)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tegangan</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Jumlah Sirkit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status Operasi</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>No Kerawanan</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sudut Pandang</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KMJNG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Kamojang</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TSBRU</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MNANG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Majenang</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BNJAR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
